--- a/public/templates/template_gate0_dalam_negeri.xlsx
+++ b/public/templates/template_gate0_dalam_negeri.xlsx
@@ -172,13 +172,13 @@
     <t>Q1</t>
   </si>
   <si>
-    <t>K1.1: Kesesuaian dengan tugas pokok dan fungsi (Tusi) Kementerian Hukum dan HAM</t>
+    <t>K1.1: Kesesuaian dengan tugas pokok dan fungsi (Tusi) Kementerian Hukum</t>
   </si>
   <si>
     <t>YA</t>
   </si>
   <si>
-    <t>Sesuai Renstra Kanwil Kemenkumham Kepri</t>
+    <t>Sesuai Renstra Kanwil Kementerian Hukum Kepri</t>
   </si>
   <si>
     <t>Q2</t>
@@ -400,7 +400,7 @@
     <t>Pemicu 7: Publikasi, Penggunaan Logo, dan Branding Resmi</t>
   </si>
   <si>
-    <t>Sesuai pedoman humas Kemenkumham</t>
+    <t>Sesuai pedoman humas Kementerian Hukum</t>
   </si>
   <si>
     <t>BAGIAN IV: CATATAN &amp; HASIL REVIU VERIFIKATOR</t>

--- a/public/templates/template_gate0_dalam_negeri.xlsx
+++ b/public/templates/template_gate0_dalam_negeri.xlsx
@@ -1160,5 +1160,13 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16:C33">
+      <formula1>"YA,TIDAK"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C35:C41">
+      <formula1>"YA,TIDAK"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>